--- a/時間（じかん）.xlsx
+++ b/時間（じかん）.xlsx
@@ -1965,7 +1965,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2071,13 +2071,6 @@
       <color rgb="FF333333"/>
       <name val="Yu Gothic"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -2225,20 +2218,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF00B0F0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -2552,148 +2532,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/時間（じかん）.xlsx
+++ b/時間（じかん）.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="478">
   <si>
     <t>相対時間</t>
   </si>
@@ -924,6 +924,30 @@
     <t>らいしゅう</t>
   </si>
   <si>
+    <t>直ちに</t>
+  </si>
+  <si>
+    <t>ただちに</t>
+  </si>
+  <si>
+    <t>前期</t>
+  </si>
+  <si>
+    <t>ぜんき</t>
+  </si>
+  <si>
+    <t>二月</t>
+  </si>
+  <si>
+    <t>にがつ</t>
+  </si>
+  <si>
+    <t>初旬</t>
+  </si>
+  <si>
+    <t>しょじゅん</t>
+  </si>
+  <si>
     <t>早速</t>
   </si>
   <si>
@@ -931,30 +955,6 @@
   </si>
   <si>
     <t>（一会儿）</t>
-  </si>
-  <si>
-    <t>前期</t>
-  </si>
-  <si>
-    <t>ぜんき</t>
-  </si>
-  <si>
-    <t>二月</t>
-  </si>
-  <si>
-    <t>にがつ</t>
-  </si>
-  <si>
-    <t>初旬</t>
-  </si>
-  <si>
-    <t>しょじゅん</t>
-  </si>
-  <si>
-    <t>間もなく</t>
-  </si>
-  <si>
-    <t>まもなく</t>
   </si>
   <si>
     <t>後期</t>
@@ -1004,6 +1004,33 @@
     <t>じょうじゅん</t>
   </si>
   <si>
+    <t>間もなく</t>
+  </si>
+  <si>
+    <t>まもなく</t>
+  </si>
+  <si>
+    <t>永遠</t>
+  </si>
+  <si>
+    <t>えいえん</t>
+  </si>
+  <si>
+    <t>（最早）</t>
+  </si>
+  <si>
+    <t>四月</t>
+  </si>
+  <si>
+    <t>しがつ</t>
+  </si>
+  <si>
+    <t>中旬</t>
+  </si>
+  <si>
+    <t>ちゅうじゅん</t>
+  </si>
+  <si>
     <t>暫く</t>
   </si>
   <si>
@@ -1013,25 +1040,22 @@
     <t>（在此之后）</t>
   </si>
   <si>
-    <t>永遠</t>
-  </si>
-  <si>
-    <t>えいえん</t>
-  </si>
-  <si>
-    <t>（最早）</t>
-  </si>
-  <si>
-    <t>四月</t>
-  </si>
-  <si>
-    <t>しがつ</t>
-  </si>
-  <si>
-    <t>中旬</t>
-  </si>
-  <si>
-    <t>ちゅうじゅん</t>
+    <t>最早</t>
+  </si>
+  <si>
+    <t>もはや</t>
+  </si>
+  <si>
+    <t>五月</t>
+  </si>
+  <si>
+    <t>ごがつ</t>
+  </si>
+  <si>
+    <t>下旬</t>
+  </si>
+  <si>
+    <t>げじゅん</t>
   </si>
   <si>
     <t>程なく</t>
@@ -1069,22 +1093,22 @@
     </r>
   </si>
   <si>
-    <t>最早</t>
-  </si>
-  <si>
-    <t>もはや</t>
-  </si>
-  <si>
-    <t>五月</t>
-  </si>
-  <si>
-    <t>ごがつ</t>
-  </si>
-  <si>
-    <t>下旬</t>
-  </si>
-  <si>
-    <t>げじゅん</t>
+    <t>最古</t>
+  </si>
+  <si>
+    <t>さいこ</t>
+  </si>
+  <si>
+    <t>六月</t>
+  </si>
+  <si>
+    <t>ろくがつ</t>
+  </si>
+  <si>
+    <t>今月</t>
+  </si>
+  <si>
+    <t>こんげつ</t>
   </si>
   <si>
     <t>つい</t>
@@ -1093,22 +1117,22 @@
     <t>（忽然，偶然）</t>
   </si>
   <si>
-    <t>最古</t>
-  </si>
-  <si>
-    <t>さいこ</t>
-  </si>
-  <si>
-    <t>六月</t>
-  </si>
-  <si>
-    <t>ろくがつ</t>
-  </si>
-  <si>
-    <t>今月</t>
-  </si>
-  <si>
-    <t>こんげつ</t>
+    <t>最近</t>
+  </si>
+  <si>
+    <t>さいきん</t>
+  </si>
+  <si>
+    <t>七月</t>
+  </si>
+  <si>
+    <t>しちがつ</t>
+  </si>
+  <si>
+    <t>半月</t>
+  </si>
+  <si>
+    <t>はんげつ</t>
   </si>
   <si>
     <t>臨時</t>
@@ -1117,22 +1141,22 @@
     <t>りんじ</t>
   </si>
   <si>
-    <t>最近</t>
-  </si>
-  <si>
-    <t>さいきん</t>
-  </si>
-  <si>
-    <t>七月</t>
-  </si>
-  <si>
-    <t>しちがつ</t>
-  </si>
-  <si>
-    <t>半月</t>
-  </si>
-  <si>
-    <t>はんげつ</t>
+    <t>期間</t>
+  </si>
+  <si>
+    <t>きかん</t>
+  </si>
+  <si>
+    <t>八月</t>
+  </si>
+  <si>
+    <t>はちがつ</t>
+  </si>
+  <si>
+    <t>再来週</t>
+  </si>
+  <si>
+    <t>さらいしゅ</t>
   </si>
   <si>
     <t>偶然</t>
@@ -1141,22 +1165,22 @@
     <t>ぐうぜん</t>
   </si>
   <si>
-    <t>期間</t>
-  </si>
-  <si>
-    <t>きかん</t>
-  </si>
-  <si>
-    <t>八月</t>
-  </si>
-  <si>
-    <t>はちがつ</t>
-  </si>
-  <si>
-    <t>再来週</t>
-  </si>
-  <si>
-    <t>さらいしゅ</t>
+    <t>永続的</t>
+  </si>
+  <si>
+    <t>えいぞくてき</t>
+  </si>
+  <si>
+    <t>九月</t>
+  </si>
+  <si>
+    <t>きゅうがつ</t>
+  </si>
+  <si>
+    <t>再来月</t>
+  </si>
+  <si>
+    <t>さらいげつ</t>
   </si>
   <si>
     <t>不図</t>
@@ -1165,22 +1189,22 @@
     <t>ふと</t>
   </si>
   <si>
-    <t>永続的</t>
-  </si>
-  <si>
-    <t>えいぞくてき</t>
-  </si>
-  <si>
-    <t>九月</t>
-  </si>
-  <si>
-    <t>きゅうがつ</t>
-  </si>
-  <si>
-    <t>再来月</t>
-  </si>
-  <si>
-    <t>さらいげつ</t>
+    <t>永久</t>
+  </si>
+  <si>
+    <t>えいきゅう</t>
+  </si>
+  <si>
+    <t>十月</t>
+  </si>
+  <si>
+    <t>じゅうがつ</t>
+  </si>
+  <si>
+    <t>半年</t>
+  </si>
+  <si>
+    <t>はんとし</t>
   </si>
   <si>
     <t>何時も</t>
@@ -1210,22 +1234,10 @@
     </r>
   </si>
   <si>
-    <t>永久</t>
-  </si>
-  <si>
-    <t>えいきゅう</t>
-  </si>
-  <si>
-    <t>十月</t>
-  </si>
-  <si>
-    <t>じゅうがつ</t>
-  </si>
-  <si>
-    <t>半年</t>
-  </si>
-  <si>
-    <t>はんとし</t>
+    <t>今年</t>
+  </si>
+  <si>
+    <t>ことし</t>
   </si>
   <si>
     <t>何時か</t>
@@ -1243,10 +1255,10 @@
     </r>
   </si>
   <si>
-    <t>今年</t>
-  </si>
-  <si>
-    <t>ことし</t>
+    <t>次年度</t>
+  </si>
+  <si>
+    <t>じねんど</t>
   </si>
   <si>
     <t>偶に</t>
@@ -1255,28 +1267,22 @@
     <t>たまに</t>
   </si>
   <si>
-    <t>次年度</t>
-  </si>
-  <si>
-    <t>じねんど</t>
-  </si>
-  <si>
     <t>再来年</t>
   </si>
   <si>
     <t>さらいねん</t>
   </si>
   <si>
+    <t>千歳</t>
+  </si>
+  <si>
+    <t>ちとせ</t>
+  </si>
+  <si>
     <t>平日</t>
   </si>
   <si>
     <t>へいじつ</t>
-  </si>
-  <si>
-    <t>千歳</t>
-  </si>
-  <si>
-    <t>ちとせ</t>
   </si>
   <si>
     <t>平常</t>
@@ -1525,6 +1531,33 @@
     <t>（在...最旺盛的时候）</t>
   </si>
   <si>
+    <t>漸く</t>
+  </si>
+  <si>
+    <t>ようやく</t>
+  </si>
+  <si>
+    <t>（渐渐地）</t>
+  </si>
+  <si>
+    <t>この度</t>
+  </si>
+  <si>
+    <t>このたび</t>
+  </si>
+  <si>
+    <t>（这次，这回）</t>
+  </si>
+  <si>
+    <t>間近い迫る</t>
+  </si>
+  <si>
+    <t>まぢかいせまる</t>
+  </si>
+  <si>
+    <t>（迫在眉睫）</t>
+  </si>
+  <si>
     <t>延長</t>
   </si>
   <si>
@@ -1685,6 +1718,12 @@
   </si>
   <si>
     <t>ゆらい</t>
+  </si>
+  <si>
+    <t>戦前</t>
+  </si>
+  <si>
+    <t>せんぜ</t>
   </si>
   <si>
     <t>♒</t>
@@ -2218,13 +2257,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF00B0F0"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -3025,7 +3064,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R58"/>
+  <dimension ref="A1:R62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="6" max="6" width="22.6666666666667" customWidth="1"/>
@@ -3780,43 +3819,43 @@
       <c r="E23" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L23" t="s">
         <v>229</v>
       </c>
-      <c r="M23" s="11" t="s">
+      <c r="M23" t="s">
         <v>230</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="N23" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="P23" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:18">
       <c r="A24" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="L24" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="M24" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>240</v>
@@ -3841,65 +3880,68 @@
       <c r="E25" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="L25" s="11" t="s">
         <v>247</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>248</v>
       </c>
       <c r="N25" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="P25" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:18">
       <c r="A26" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="P26" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="Q26" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:18">
       <c r="A27" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>265</v>
       </c>
       <c r="M27" s="2" t="s">
@@ -3928,14 +3970,11 @@
       <c r="E28" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="N28" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>276</v>
@@ -3963,6 +4002,9 @@
       <c r="M29" s="2" t="s">
         <v>283</v>
       </c>
+      <c r="N29" s="2" t="s">
+        <v>275</v>
+      </c>
       <c r="P29" s="2" t="s">
         <v>284</v>
       </c>
@@ -4015,34 +4057,31 @@
       <c r="M31" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="N31" s="5" t="s">
+      <c r="P31" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="Q31" s="8" t="s">
         <v>301</v>
-      </c>
-      <c r="Q31" s="8" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:18">
       <c r="A32" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="N32" s="5" t="s">
         <v>308</v>
@@ -4056,10 +4095,13 @@
         <v>310</v>
       </c>
       <c r="I33" s="2"/>
-      <c r="L33" s="12" t="s">
+      <c r="L33" s="2" t="s">
         <v>311</v>
       </c>
       <c r="M33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N33" s="5" t="s">
         <v>312</v>
       </c>
     </row>
@@ -4070,25 +4112,25 @@
       <c r="E34" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="L34" s="2" t="s">
-        <v>205</v>
+      <c r="L34" s="12" t="s">
+        <v>315</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>206</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" ht="18" spans="4:15">
       <c r="D35" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="L35" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="M35" s="7" t="s">
         <v>318</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="36" ht="18" spans="4:15">
@@ -4098,62 +4140,62 @@
       <c r="E36" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="L36" s="7" t="s">
+      <c r="L36" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="M36" s="13" t="s">
+      <c r="M36" s="7" t="s">
         <v>322</v>
-      </c>
-      <c r="N36" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="37" ht="18" spans="4:15">
       <c r="L37" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="M37" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="M37" s="7" t="s">
+      <c r="N37" t="s">
         <v>325</v>
       </c>
-      <c r="N37" s="5" t="s">
+    </row>
+    <row r="38" ht="18" spans="4:15">
+      <c r="L38" s="7" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="38" ht="18" spans="4:15">
-      <c r="L38" s="13" t="s">
+      <c r="M38" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="M38" s="13" t="s">
+      <c r="N38" s="5" t="s">
         <v>328</v>
       </c>
-      <c r="N38" s="14" t="s">
+    </row>
+    <row r="39" ht="18" spans="4:15">
+      <c r="L39" s="13" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="39" ht="18" spans="4:15">
-      <c r="L39" s="7" t="s">
+      <c r="M39" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="M39" s="7" t="s">
+      <c r="N39" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="N39" s="14" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="40" ht="15.6" spans="4:15">
-      <c r="L40" s="8" t="s">
+    </row>
+    <row r="40" ht="18" spans="4:15">
+      <c r="L40" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="M40" s="8" t="s">
+      <c r="M40" s="7" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="41" ht="18" spans="4:15">
-      <c r="L41" s="7" t="s">
+      <c r="N40" s="14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="41" ht="15.6" spans="4:15">
+      <c r="L41" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="M41" s="7" t="s">
+      <c r="M41" s="8" t="s">
         <v>335</v>
       </c>
     </row>
@@ -4164,15 +4206,15 @@
       <c r="M42" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="N42" s="15" t="s">
+    </row>
+    <row r="43" ht="18" spans="4:15">
+      <c r="L43" s="7" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="43" ht="18" spans="4:15">
-      <c r="L43" s="2" t="s">
+      <c r="M43" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="N43" s="15" t="s">
         <v>340</v>
       </c>
     </row>
@@ -4183,64 +4225,64 @@
       <c r="M44" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="N44" t="s">
+    </row>
+    <row r="45" ht="18" spans="4:15">
+      <c r="L45" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="O44" t="s">
+      <c r="M45" s="2" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="45" ht="18" spans="4:15">
-      <c r="L45" s="7" t="s">
+      <c r="N45" t="s">
         <v>345</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="O45" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="46" ht="15" spans="4:15">
-      <c r="L46" s="16" t="s">
+    <row r="46" ht="18" spans="4:15">
+      <c r="L46" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="M46" s="17" t="s">
+      <c r="M46" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="N46" t="s">
+    </row>
+    <row r="47" ht="15" spans="4:15">
+      <c r="L47" s="16" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="47" ht="18" spans="4:15">
-      <c r="L47" t="s">
+      <c r="M47" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="M47" s="18" t="s">
+      <c r="N47" t="s">
         <v>351</v>
       </c>
-      <c r="O47" s="2" t="s">
+    </row>
+    <row r="48" ht="18" spans="4:15">
+      <c r="L48" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="48" ht="16.2" spans="4:15">
-      <c r="L48" s="19" t="s">
+      <c r="M48" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="49" ht="16.2" spans="12:14">
+      <c r="L49" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M48" s="18" t="s">
+      <c r="M49" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="49" ht="15.6" spans="12:14">
-      <c r="L49" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="M49" s="8" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="50" ht="18" spans="12:14">
-      <c r="L50" s="2" t="s">
+    <row r="50" ht="15.6" spans="12:14">
+      <c r="L50" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="M50" s="8" t="s">
         <v>356</v>
       </c>
     </row>
@@ -4267,19 +4309,16 @@
       <c r="M53" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="N53" s="15" t="s">
-        <v>363</v>
-      </c>
     </row>
     <row r="54" ht="18" spans="12:14">
       <c r="L54" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="M54" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="N54" s="15" t="s">
         <v>365</v>
-      </c>
-      <c r="N54" s="15" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="55" ht="18" spans="12:14">
@@ -4289,38 +4328,82 @@
       <c r="M55" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="N55" s="3" t="s">
-        <v>368</v>
+      <c r="N55" s="15" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="56" ht="18" spans="12:14">
       <c r="L56" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="M56" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="N56" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="57" ht="18" spans="12:14">
       <c r="L57" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="M57" t="s">
+      <c r="N57" s="3" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="58" spans="12:14">
-      <c r="L58" t="s">
+    <row r="58" ht="18" spans="12:14">
+      <c r="L58" s="2" t="s">
         <v>374</v>
       </c>
       <c r="M58" t="s">
         <v>375</v>
       </c>
-      <c r="N58" t="s">
+    </row>
+    <row r="59" spans="12:14">
+      <c r="L59" t="s">
         <v>376</v>
+      </c>
+      <c r="M59" t="s">
+        <v>377</v>
+      </c>
+      <c r="N59" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="60" spans="12:14">
+      <c r="L60" t="s">
+        <v>379</v>
+      </c>
+      <c r="M60" t="s">
+        <v>380</v>
+      </c>
+      <c r="N60" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="61" spans="12:14">
+      <c r="L61" t="s">
+        <v>382</v>
+      </c>
+      <c r="M61" t="s">
+        <v>383</v>
+      </c>
+      <c r="N61" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="62" spans="12:14">
+      <c r="L62" t="s">
+        <v>385</v>
+      </c>
+      <c r="M62" t="s">
+        <v>386</v>
+      </c>
+      <c r="N62" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -4340,69 +4423,69 @@
   <sheetData>
     <row r="2" ht="18" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="H2" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:9">
       <c r="A3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" ht="18" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:9">
@@ -4425,39 +4508,39 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="C5" s="6">
         <v>11293</v>
@@ -4465,67 +4548,67 @@
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="C9" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="C10" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="C11" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -4537,23 +4620,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A2:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>424</v>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B4" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -4575,136 +4666,136 @@
   <sheetData>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>435</v>
+        <v>448</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>437</v>
+        <v>450</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>438</v>
+        <v>451</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>

--- a/時間（じかん）.xlsx
+++ b/時間（じかん）.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="480">
   <si>
     <t>相対時間</t>
   </si>
@@ -1390,6 +1390,12 @@
       </rPr>
       <t>久违）</t>
     </r>
+  </si>
+  <si>
+    <t>当時</t>
+  </si>
+  <si>
+    <t>とうじ</t>
   </si>
   <si>
     <t>随時</t>
@@ -2257,13 +2263,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF00B0F0"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -3064,7 +3070,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R62"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="6" max="6" width="22.6666666666667" customWidth="1"/>
@@ -4218,11 +4224,11 @@
         <v>340</v>
       </c>
     </row>
-    <row r="44" ht="18" spans="4:15">
-      <c r="L44" s="2" t="s">
+    <row r="44" spans="4:15">
+      <c r="L44" t="s">
         <v>341</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="M44" t="s">
         <v>342</v>
       </c>
     </row>
@@ -4233,68 +4239,68 @@
       <c r="M45" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="N45" t="s">
+    </row>
+    <row r="46" ht="18" spans="4:15">
+      <c r="L46" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="O45" t="s">
+      <c r="M46" s="2" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="46" ht="18" spans="4:15">
-      <c r="L46" s="7" t="s">
+      <c r="N46" t="s">
         <v>347</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="O46" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="47" ht="15" spans="4:15">
-      <c r="L47" s="16" t="s">
+    <row r="47" ht="18" spans="4:15">
+      <c r="L47" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="M47" s="17" t="s">
+      <c r="M47" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="N47" t="s">
+    </row>
+    <row r="48" ht="15" spans="4:15">
+      <c r="L48" s="16" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="48" ht="18" spans="4:15">
-      <c r="L48" t="s">
+      <c r="M48" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="M48" s="18" t="s">
+      <c r="N48" t="s">
         <v>353</v>
       </c>
-      <c r="O48" s="2" t="s">
+    </row>
+    <row r="49" ht="18" spans="12:15">
+      <c r="L49" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="49" ht="16.2" spans="12:14">
-      <c r="L49" s="19" t="s">
+      <c r="M49" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="50" ht="16.2" spans="12:15">
+      <c r="L50" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M49" s="18" t="s">
+      <c r="M50" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" ht="15.6" spans="12:14">
-      <c r="L50" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="M50" s="8" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="51" ht="18" spans="12:14">
-      <c r="L51" s="2" t="s">
+    <row r="51" ht="15.6" spans="12:15">
+      <c r="L51" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="M51" s="8" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="52" ht="18" spans="12:14">
+    <row r="52" ht="18" spans="12:15">
       <c r="L52" s="2" t="s">
         <v>359</v>
       </c>
@@ -4302,7 +4308,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="53" ht="18" spans="12:14">
+    <row r="53" ht="18" spans="12:15">
       <c r="L53" s="2" t="s">
         <v>361</v>
       </c>
@@ -4310,100 +4316,108 @@
         <v>362</v>
       </c>
     </row>
-    <row r="54" ht="18" spans="12:14">
+    <row r="54" ht="18" spans="12:15">
       <c r="L54" s="2" t="s">
         <v>363</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="N54" s="15" t="s">
+    </row>
+    <row r="55" ht="18" spans="12:15">
+      <c r="L55" s="2" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="55" ht="18" spans="12:14">
-      <c r="L55" s="2" t="s">
+      <c r="M55" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="N55" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="N55" s="15" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="56" ht="18" spans="12:14">
+    </row>
+    <row r="56" ht="18" spans="12:15">
       <c r="L56" s="2" t="s">
         <v>368</v>
       </c>
       <c r="M56" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="N56" s="3" t="s">
+      <c r="N56" s="15" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="57" ht="18" spans="12:15">
+      <c r="L57" s="2" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="57" ht="18" spans="12:14">
-      <c r="L57" s="2" t="s">
+      <c r="M57" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="N57" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="N57" s="3" t="s">
+    </row>
+    <row r="58" ht="18" spans="12:15">
+      <c r="L58" s="2" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="58" ht="18" spans="12:14">
-      <c r="L58" s="2" t="s">
+      <c r="M58" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="M58" t="s">
+      <c r="N58" s="3" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="59" spans="12:14">
-      <c r="L59" t="s">
+    <row r="59" ht="18" spans="12:15">
+      <c r="L59" s="2" t="s">
         <v>376</v>
       </c>
       <c r="M59" t="s">
         <v>377</v>
       </c>
-      <c r="N59" t="s">
+    </row>
+    <row r="60" spans="12:15">
+      <c r="L60" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="60" spans="12:14">
-      <c r="L60" t="s">
+      <c r="M60" t="s">
         <v>379</v>
       </c>
-      <c r="M60" t="s">
+      <c r="N60" t="s">
         <v>380</v>
       </c>
-      <c r="N60" t="s">
+    </row>
+    <row r="61" spans="12:15">
+      <c r="L61" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="61" spans="12:14">
-      <c r="L61" t="s">
+      <c r="M61" t="s">
         <v>382</v>
       </c>
-      <c r="M61" t="s">
+      <c r="N61" t="s">
         <v>383</v>
       </c>
-      <c r="N61" t="s">
+    </row>
+    <row r="62" spans="12:15">
+      <c r="L62" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="62" spans="12:14">
-      <c r="L62" t="s">
+      <c r="M62" t="s">
         <v>385</v>
       </c>
-      <c r="M62" t="s">
+      <c r="N62" t="s">
         <v>386</v>
       </c>
-      <c r="N62" t="s">
+    </row>
+    <row r="63" spans="12:15">
+      <c r="L63" t="s">
         <v>387</v>
+      </c>
+      <c r="M63" t="s">
+        <v>388</v>
+      </c>
+      <c r="N63" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -4423,69 +4437,69 @@
   <sheetData>
     <row r="2" ht="18" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:9">
       <c r="A3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" ht="18" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:9">
@@ -4508,39 +4522,39 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C5" s="6">
         <v>11293</v>
@@ -4548,67 +4562,67 @@
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -4625,26 +4639,26 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -4666,136 +4680,136 @@
   <sheetData>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>

--- a/時間（じかん）.xlsx
+++ b/時間（じかん）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="基礎（きそ）" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="486">
   <si>
     <t>相対時間</t>
   </si>
@@ -1031,6 +1031,33 @@
     <t>ちゅうじゅん</t>
   </si>
   <si>
+    <t>軈て</t>
+  </si>
+  <si>
+    <t>やがて</t>
+  </si>
+  <si>
+    <t>（不久，即将）</t>
+  </si>
+  <si>
+    <t>最早</t>
+  </si>
+  <si>
+    <t>もはや</t>
+  </si>
+  <si>
+    <t>五月</t>
+  </si>
+  <si>
+    <t>ごがつ</t>
+  </si>
+  <si>
+    <t>下旬</t>
+  </si>
+  <si>
+    <t>げじゅん</t>
+  </si>
+  <si>
     <t>暫く</t>
   </si>
   <si>
@@ -1040,22 +1067,22 @@
     <t>（在此之后）</t>
   </si>
   <si>
-    <t>最早</t>
-  </si>
-  <si>
-    <t>もはや</t>
-  </si>
-  <si>
-    <t>五月</t>
-  </si>
-  <si>
-    <t>ごがつ</t>
-  </si>
-  <si>
-    <t>下旬</t>
-  </si>
-  <si>
-    <t>げじゅん</t>
+    <t>最古</t>
+  </si>
+  <si>
+    <t>さいこ</t>
+  </si>
+  <si>
+    <t>六月</t>
+  </si>
+  <si>
+    <t>ろくがつ</t>
+  </si>
+  <si>
+    <t>今月</t>
+  </si>
+  <si>
+    <t>こんげつ</t>
   </si>
   <si>
     <t>程なく</t>
@@ -1093,22 +1120,22 @@
     </r>
   </si>
   <si>
-    <t>最古</t>
-  </si>
-  <si>
-    <t>さいこ</t>
-  </si>
-  <si>
-    <t>六月</t>
-  </si>
-  <si>
-    <t>ろくがつ</t>
-  </si>
-  <si>
-    <t>今月</t>
-  </si>
-  <si>
-    <t>こんげつ</t>
+    <t>最近</t>
+  </si>
+  <si>
+    <t>さいきん</t>
+  </si>
+  <si>
+    <t>七月</t>
+  </si>
+  <si>
+    <t>しちがつ</t>
+  </si>
+  <si>
+    <t>半月</t>
+  </si>
+  <si>
+    <t>はんげつ</t>
   </si>
   <si>
     <t>つい</t>
@@ -1117,22 +1144,22 @@
     <t>（忽然，偶然）</t>
   </si>
   <si>
-    <t>最近</t>
-  </si>
-  <si>
-    <t>さいきん</t>
-  </si>
-  <si>
-    <t>七月</t>
-  </si>
-  <si>
-    <t>しちがつ</t>
-  </si>
-  <si>
-    <t>半月</t>
-  </si>
-  <si>
-    <t>はんげつ</t>
+    <t>期間</t>
+  </si>
+  <si>
+    <t>きかん</t>
+  </si>
+  <si>
+    <t>八月</t>
+  </si>
+  <si>
+    <t>はちがつ</t>
+  </si>
+  <si>
+    <t>再来週</t>
+  </si>
+  <si>
+    <t>さらいしゅ</t>
   </si>
   <si>
     <t>臨時</t>
@@ -1141,22 +1168,22 @@
     <t>りんじ</t>
   </si>
   <si>
-    <t>期間</t>
-  </si>
-  <si>
-    <t>きかん</t>
-  </si>
-  <si>
-    <t>八月</t>
-  </si>
-  <si>
-    <t>はちがつ</t>
-  </si>
-  <si>
-    <t>再来週</t>
-  </si>
-  <si>
-    <t>さらいしゅ</t>
+    <t>永続的</t>
+  </si>
+  <si>
+    <t>えいぞくてき</t>
+  </si>
+  <si>
+    <t>九月</t>
+  </si>
+  <si>
+    <t>きゅうがつ</t>
+  </si>
+  <si>
+    <t>再来月</t>
+  </si>
+  <si>
+    <t>さらいげつ</t>
   </si>
   <si>
     <t>偶然</t>
@@ -1165,22 +1192,22 @@
     <t>ぐうぜん</t>
   </si>
   <si>
-    <t>永続的</t>
-  </si>
-  <si>
-    <t>えいぞくてき</t>
-  </si>
-  <si>
-    <t>九月</t>
-  </si>
-  <si>
-    <t>きゅうがつ</t>
-  </si>
-  <si>
-    <t>再来月</t>
-  </si>
-  <si>
-    <t>さらいげつ</t>
+    <t>永久</t>
+  </si>
+  <si>
+    <t>えいきゅう</t>
+  </si>
+  <si>
+    <t>十月</t>
+  </si>
+  <si>
+    <t>じゅうがつ</t>
+  </si>
+  <si>
+    <t>半年</t>
+  </si>
+  <si>
+    <t>はんとし</t>
   </si>
   <si>
     <t>不図</t>
@@ -1189,22 +1216,10 @@
     <t>ふと</t>
   </si>
   <si>
-    <t>永久</t>
-  </si>
-  <si>
-    <t>えいきゅう</t>
-  </si>
-  <si>
-    <t>十月</t>
-  </si>
-  <si>
-    <t>じゅうがつ</t>
-  </si>
-  <si>
-    <t>半年</t>
-  </si>
-  <si>
-    <t>はんとし</t>
+    <t>今年</t>
+  </si>
+  <si>
+    <t>ことし</t>
   </si>
   <si>
     <t>何時も</t>
@@ -1234,10 +1249,10 @@
     </r>
   </si>
   <si>
-    <t>今年</t>
-  </si>
-  <si>
-    <t>ことし</t>
+    <t>次年度</t>
+  </si>
+  <si>
+    <t>じねんど</t>
   </si>
   <si>
     <t>何時か</t>
@@ -1255,22 +1270,16 @@
     </r>
   </si>
   <si>
-    <t>次年度</t>
-  </si>
-  <si>
-    <t>じねんど</t>
+    <t>再来年</t>
+  </si>
+  <si>
+    <t>さらいねん</t>
   </si>
   <si>
     <t>偶に</t>
   </si>
   <si>
     <t>たまに</t>
-  </si>
-  <si>
-    <t>再来年</t>
-  </si>
-  <si>
-    <t>さらいねん</t>
   </si>
   <si>
     <t>千歳</t>
@@ -1562,6 +1571,15 @@
   </si>
   <si>
     <t>（迫在眉睫）</t>
+  </si>
+  <si>
+    <t>半ば</t>
+  </si>
+  <si>
+    <t>なかば</t>
+  </si>
+  <si>
+    <t>（中途，一半）</t>
   </si>
   <si>
     <t>延長</t>
@@ -3070,7 +3088,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R63"/>
+  <dimension ref="A1:R65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="6" max="6" width="22.6666666666667" customWidth="1"/>
@@ -3918,7 +3936,7 @@
       <c r="E26" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="L26" s="11" t="s">
         <v>256</v>
       </c>
       <c r="M26" s="2" t="s">
@@ -3976,120 +3994,120 @@
       <c r="E28" s="2" t="s">
         <v>273</v>
       </c>
+      <c r="L28" s="2" t="s">
+        <v>274</v>
+      </c>
       <c r="M28" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:18">
       <c r="A29" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="L29" s="2" t="s">
         <v>282</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>283</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:18">
       <c r="A30" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>284</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:18">
       <c r="A31" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q31" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:18">
       <c r="A32" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="N32" s="5" t="s">
         <v>308</v>
       </c>
     </row>
@@ -4105,62 +4123,62 @@
         <v>311</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>48</v>
+        <v>312</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" ht="18" spans="4:15">
       <c r="D34" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="L34" s="12" t="s">
         <v>315</v>
       </c>
+      <c r="L34" s="2" t="s">
+        <v>316</v>
+      </c>
       <c r="M34" s="2" t="s">
-        <v>316</v>
+        <v>48</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="35" ht="18" spans="4:15">
       <c r="D35" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>205</v>
+        <v>319</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>320</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>206</v>
+        <v>321</v>
       </c>
     </row>
     <row r="36" ht="18" spans="4:15">
       <c r="D36" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="L36" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="M36" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="37" ht="18" spans="4:15">
-      <c r="L37" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="M37" s="13" t="s">
+      <c r="L37" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="N37" t="s">
+      <c r="M37" s="7" t="s">
         <v>325</v>
       </c>
     </row>
@@ -4168,170 +4186,170 @@
       <c r="L38" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="M38" s="7" t="s">
+      <c r="M38" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="N38" s="5" t="s">
+      <c r="N38" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="39" ht="18" spans="4:15">
-      <c r="L39" s="13" t="s">
+      <c r="L39" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="M39" s="13" t="s">
+      <c r="M39" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="N39" s="14" t="s">
+      <c r="N39" s="5" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="40" ht="18" spans="4:15">
-      <c r="L40" s="7" t="s">
+      <c r="L40" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="M40" s="7" t="s">
+      <c r="M40" s="13" t="s">
         <v>333</v>
       </c>
       <c r="N40" s="14" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="41" ht="15.6" spans="4:15">
-      <c r="L41" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="M41" s="8" t="s">
+    </row>
+    <row r="41" ht="18" spans="4:15">
+      <c r="L41" s="7" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="42" ht="18" spans="4:15">
-      <c r="L42" s="7" t="s">
+      <c r="M41" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="M42" s="7" t="s">
+      <c r="N41" s="14" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="42" ht="15.6" spans="4:15">
+      <c r="L42" s="8" t="s">
         <v>337</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="43" ht="18" spans="4:15">
       <c r="L43" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="N43" s="15" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="44" spans="4:15">
-      <c r="L44" t="s">
+    <row r="44" ht="18" spans="4:15">
+      <c r="L44" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="M44" t="s">
+      <c r="M44" s="7" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="45" ht="18" spans="4:15">
-      <c r="L45" s="2" t="s">
+      <c r="N44" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="M45" s="2" t="s">
+    </row>
+    <row r="45" spans="4:15">
+      <c r="L45" t="s">
         <v>344</v>
+      </c>
+      <c r="M45" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="46" ht="18" spans="4:15">
       <c r="L46" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="N46" t="s">
         <v>347</v>
       </c>
-      <c r="O46" t="s">
+    </row>
+    <row r="47" ht="18" spans="4:15">
+      <c r="L47" s="2" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="47" ht="18" spans="4:15">
-      <c r="L47" s="7" t="s">
+      <c r="M47" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="N47" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="48" ht="15" spans="4:15">
-      <c r="L48" s="16" t="s">
+      <c r="O47" t="s">
         <v>351</v>
       </c>
-      <c r="M48" s="17" t="s">
+    </row>
+    <row r="48" ht="18" spans="4:15">
+      <c r="L48" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="N48" t="s">
+      <c r="M48" s="2" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="49" ht="18" spans="12:15">
-      <c r="L49" t="s">
+    <row r="49" ht="15" spans="12:15">
+      <c r="L49" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="M49" s="18" t="s">
+      <c r="M49" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="O49" s="2" t="s">
+      <c r="N49" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="50" ht="16.2" spans="12:15">
-      <c r="L50" s="19" t="s">
+    <row r="50" ht="18" spans="12:15">
+      <c r="L50" t="s">
+        <v>357</v>
+      </c>
+      <c r="M50" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="51" ht="16.2" spans="12:15">
+      <c r="L51" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M50" s="18" t="s">
+      <c r="M51" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="51" ht="15.6" spans="12:15">
-      <c r="L51" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="M51" s="8" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="52" ht="18" spans="12:15">
-      <c r="L52" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="M52" s="2" t="s">
+    <row r="52" ht="15.6" spans="12:15">
+      <c r="L52" s="8" t="s">
         <v>360</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="53" ht="18" spans="12:15">
       <c r="L53" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" ht="18" spans="12:15">
       <c r="L54" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="55" ht="18" spans="12:15">
       <c r="L55" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="N55" s="15" t="s">
         <v>367</v>
       </c>
     </row>
@@ -4343,18 +4361,18 @@
         <v>369</v>
       </c>
       <c r="N56" s="15" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="57" ht="18" spans="12:15">
       <c r="L57" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="N57" s="15" t="s">
         <v>370</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="58" ht="18" spans="12:15">
@@ -4372,18 +4390,18 @@
       <c r="L59" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="M59" t="s">
+      <c r="M59" s="2" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="60" spans="12:15">
-      <c r="L60" t="s">
+      <c r="N59" s="3" t="s">
         <v>378</v>
       </c>
+    </row>
+    <row r="60" ht="18" spans="12:15">
+      <c r="L60" s="2" t="s">
+        <v>379</v>
+      </c>
       <c r="M60" t="s">
-        <v>379</v>
-      </c>
-      <c r="N60" t="s">
         <v>380</v>
       </c>
     </row>
@@ -4418,6 +4436,28 @@
       </c>
       <c r="N63" t="s">
         <v>389</v>
+      </c>
+    </row>
+    <row r="64" spans="12:15">
+      <c r="L64" t="s">
+        <v>390</v>
+      </c>
+      <c r="M64" t="s">
+        <v>391</v>
+      </c>
+      <c r="N64" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="65" spans="12:14">
+      <c r="L65" t="s">
+        <v>393</v>
+      </c>
+      <c r="M65" t="s">
+        <v>394</v>
+      </c>
+      <c r="N65" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -4437,69 +4477,69 @@
   <sheetData>
     <row r="2" ht="18" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="H2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:9">
       <c r="A3" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" ht="18" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:9">
@@ -4522,39 +4562,39 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C5" s="6">
         <v>11293</v>
@@ -4562,67 +4602,67 @@
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C9" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C10" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C11" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -4639,26 +4679,26 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B4" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -4680,136 +4720,136 @@
   <sheetData>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/時間（じかん）.xlsx
+++ b/時間（じかん）.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="487">
   <si>
     <t>相対時間</t>
   </si>
@@ -871,10 +871,7 @@
     <t>まいしゅ</t>
   </si>
   <si>
-    <t>行き成り</t>
-  </si>
-  <si>
-    <t>いきなり</t>
+    <t>そっと</t>
   </si>
   <si>
     <r>
@@ -924,37 +921,34 @@
     <t>らいしゅう</t>
   </si>
   <si>
+    <t>行き成り</t>
+  </si>
+  <si>
+    <t>いきなり</t>
+  </si>
+  <si>
+    <t>前期</t>
+  </si>
+  <si>
+    <t>ぜんき</t>
+  </si>
+  <si>
+    <t>二月</t>
+  </si>
+  <si>
+    <t>にがつ</t>
+  </si>
+  <si>
+    <t>初旬</t>
+  </si>
+  <si>
+    <t>しょじゅん</t>
+  </si>
+  <si>
     <t>直ちに</t>
   </si>
   <si>
     <t>ただちに</t>
-  </si>
-  <si>
-    <t>前期</t>
-  </si>
-  <si>
-    <t>ぜんき</t>
-  </si>
-  <si>
-    <t>二月</t>
-  </si>
-  <si>
-    <t>にがつ</t>
-  </si>
-  <si>
-    <t>初旬</t>
-  </si>
-  <si>
-    <t>しょじゅん</t>
-  </si>
-  <si>
-    <t>早速</t>
-  </si>
-  <si>
-    <t>さっそく</t>
-  </si>
-  <si>
-    <t>（一会儿）</t>
   </si>
   <si>
     <t>後期</t>
@@ -1004,31 +998,58 @@
     <t>じょうじゅん</t>
   </si>
   <si>
+    <t>早速</t>
+  </si>
+  <si>
+    <t>さっそく</t>
+  </si>
+  <si>
+    <t>（一会儿）</t>
+  </si>
+  <si>
+    <t>永遠</t>
+  </si>
+  <si>
+    <t>えいえん</t>
+  </si>
+  <si>
+    <t>（最早）</t>
+  </si>
+  <si>
+    <t>四月</t>
+  </si>
+  <si>
+    <t>しがつ</t>
+  </si>
+  <si>
+    <t>中旬</t>
+  </si>
+  <si>
+    <t>ちゅうじゅん</t>
+  </si>
+  <si>
     <t>間もなく</t>
   </si>
   <si>
     <t>まもなく</t>
   </si>
   <si>
-    <t>永遠</t>
-  </si>
-  <si>
-    <t>えいえん</t>
-  </si>
-  <si>
-    <t>（最早）</t>
-  </si>
-  <si>
-    <t>四月</t>
-  </si>
-  <si>
-    <t>しがつ</t>
-  </si>
-  <si>
-    <t>中旬</t>
-  </si>
-  <si>
-    <t>ちゅうじゅん</t>
+    <t>最早</t>
+  </si>
+  <si>
+    <t>もはや</t>
+  </si>
+  <si>
+    <t>五月</t>
+  </si>
+  <si>
+    <t>ごがつ</t>
+  </si>
+  <si>
+    <t>下旬</t>
+  </si>
+  <si>
+    <t>げじゅん</t>
   </si>
   <si>
     <t>軈て</t>
@@ -1040,22 +1061,22 @@
     <t>（不久，即将）</t>
   </si>
   <si>
-    <t>最早</t>
-  </si>
-  <si>
-    <t>もはや</t>
-  </si>
-  <si>
-    <t>五月</t>
-  </si>
-  <si>
-    <t>ごがつ</t>
-  </si>
-  <si>
-    <t>下旬</t>
-  </si>
-  <si>
-    <t>げじゅん</t>
+    <t>最古</t>
+  </si>
+  <si>
+    <t>さいこ</t>
+  </si>
+  <si>
+    <t>六月</t>
+  </si>
+  <si>
+    <t>ろくがつ</t>
+  </si>
+  <si>
+    <t>今月</t>
+  </si>
+  <si>
+    <t>こんげつ</t>
   </si>
   <si>
     <t>暫く</t>
@@ -1067,22 +1088,22 @@
     <t>（在此之后）</t>
   </si>
   <si>
-    <t>最古</t>
-  </si>
-  <si>
-    <t>さいこ</t>
-  </si>
-  <si>
-    <t>六月</t>
-  </si>
-  <si>
-    <t>ろくがつ</t>
-  </si>
-  <si>
-    <t>今月</t>
-  </si>
-  <si>
-    <t>こんげつ</t>
+    <t>最近</t>
+  </si>
+  <si>
+    <t>さいきん</t>
+  </si>
+  <si>
+    <t>七月</t>
+  </si>
+  <si>
+    <t>しちがつ</t>
+  </si>
+  <si>
+    <t>半月</t>
+  </si>
+  <si>
+    <t>はんげつ</t>
   </si>
   <si>
     <t>程なく</t>
@@ -1120,22 +1141,22 @@
     </r>
   </si>
   <si>
-    <t>最近</t>
-  </si>
-  <si>
-    <t>さいきん</t>
-  </si>
-  <si>
-    <t>七月</t>
-  </si>
-  <si>
-    <t>しちがつ</t>
-  </si>
-  <si>
-    <t>半月</t>
-  </si>
-  <si>
-    <t>はんげつ</t>
+    <t>期間</t>
+  </si>
+  <si>
+    <t>きかん</t>
+  </si>
+  <si>
+    <t>八月</t>
+  </si>
+  <si>
+    <t>はちがつ</t>
+  </si>
+  <si>
+    <t>再来週</t>
+  </si>
+  <si>
+    <t>さらいしゅ</t>
   </si>
   <si>
     <t>つい</t>
@@ -1144,22 +1165,22 @@
     <t>（忽然，偶然）</t>
   </si>
   <si>
-    <t>期間</t>
-  </si>
-  <si>
-    <t>きかん</t>
-  </si>
-  <si>
-    <t>八月</t>
-  </si>
-  <si>
-    <t>はちがつ</t>
-  </si>
-  <si>
-    <t>再来週</t>
-  </si>
-  <si>
-    <t>さらいしゅ</t>
+    <t>永続的</t>
+  </si>
+  <si>
+    <t>えいぞくてき</t>
+  </si>
+  <si>
+    <t>九月</t>
+  </si>
+  <si>
+    <t>きゅうがつ</t>
+  </si>
+  <si>
+    <t>再来月</t>
+  </si>
+  <si>
+    <t>さらいげつ</t>
   </si>
   <si>
     <t>臨時</t>
@@ -1168,22 +1189,22 @@
     <t>りんじ</t>
   </si>
   <si>
-    <t>永続的</t>
-  </si>
-  <si>
-    <t>えいぞくてき</t>
-  </si>
-  <si>
-    <t>九月</t>
-  </si>
-  <si>
-    <t>きゅうがつ</t>
-  </si>
-  <si>
-    <t>再来月</t>
-  </si>
-  <si>
-    <t>さらいげつ</t>
+    <t>永久</t>
+  </si>
+  <si>
+    <t>えいきゅう</t>
+  </si>
+  <si>
+    <t>十月</t>
+  </si>
+  <si>
+    <t>じゅうがつ</t>
+  </si>
+  <si>
+    <t>半年</t>
+  </si>
+  <si>
+    <t>はんとし</t>
   </si>
   <si>
     <t>偶然</t>
@@ -1192,22 +1213,10 @@
     <t>ぐうぜん</t>
   </si>
   <si>
-    <t>永久</t>
-  </si>
-  <si>
-    <t>えいきゅう</t>
-  </si>
-  <si>
-    <t>十月</t>
-  </si>
-  <si>
-    <t>じゅうがつ</t>
-  </si>
-  <si>
-    <t>半年</t>
-  </si>
-  <si>
-    <t>はんとし</t>
+    <t>今年</t>
+  </si>
+  <si>
+    <t>ことし</t>
   </si>
   <si>
     <t>不図</t>
@@ -1216,10 +1225,10 @@
     <t>ふと</t>
   </si>
   <si>
-    <t>今年</t>
-  </si>
-  <si>
-    <t>ことし</t>
+    <t>次年度</t>
+  </si>
+  <si>
+    <t>じねんど</t>
   </si>
   <si>
     <t>何時も</t>
@@ -1249,10 +1258,10 @@
     </r>
   </si>
   <si>
-    <t>次年度</t>
-  </si>
-  <si>
-    <t>じねんど</t>
+    <t>再来年</t>
+  </si>
+  <si>
+    <t>さらいねん</t>
   </si>
   <si>
     <t>何時か</t>
@@ -1270,22 +1279,16 @@
     </r>
   </si>
   <si>
-    <t>再来年</t>
-  </si>
-  <si>
-    <t>さらいねん</t>
+    <t>千歳</t>
+  </si>
+  <si>
+    <t>ちとせ</t>
   </si>
   <si>
     <t>偶に</t>
   </si>
   <si>
     <t>たまに</t>
-  </si>
-  <si>
-    <t>千歳</t>
-  </si>
-  <si>
-    <t>ちとせ</t>
   </si>
   <si>
     <t>平日</t>
@@ -1413,6 +1416,9 @@
     <t>ずいじ</t>
   </si>
   <si>
+    <t>定期に開催する：定期举行</t>
+  </si>
+  <si>
     <t>定期に</t>
   </si>
   <si>
@@ -1422,9 +1428,6 @@
     <t>（定时的）</t>
   </si>
   <si>
-    <t>定期に開催する：定期举行</t>
-  </si>
-  <si>
     <t>久しぶり</t>
   </si>
   <si>
@@ -1440,13 +1443,13 @@
     <t>（正在…中,正在…的时候）</t>
   </si>
   <si>
+    <t>頃｜ころ</t>
+  </si>
+  <si>
     <t>終わる</t>
   </si>
   <si>
     <t>おわる</t>
-  </si>
-  <si>
-    <t>頃｜ころ</t>
   </si>
   <si>
     <t>最中</t>
@@ -2281,13 +2284,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B0F0"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF00B0F0"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -3088,7 +3091,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="6" max="6" width="22.6666666666667" customWidth="1"/>
@@ -3814,650 +3817,659 @@
       <c r="E22" t="s">
         <v>219</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="L22" s="2"/>
+      <c r="M22" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="N22" s="11" t="s">
+      <c r="P22" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:18">
       <c r="A23" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="L23" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="P23" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="N23" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:18">
       <c r="A24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="L24" t="s">
         <v>236</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="M24" t="s">
         <v>237</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="N24" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="P24" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:18">
       <c r="A25" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="L25" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="M25" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="N25" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="N25" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="P25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:18">
       <c r="A26" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="L26" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="M26" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="P26" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="Q26" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:18">
       <c r="A27" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="L27" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="Q27" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:18">
       <c r="A28" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="L28" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="N28" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="P28" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="Q28" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:18">
       <c r="A29" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="L29" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="M29" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:18">
       <c r="A30" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="P30" s="2" t="s">
+      <c r="Q30" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:18">
       <c r="A31" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="L31" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="P31" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="Q31" s="8" t="s">
         <v>301</v>
-      </c>
-      <c r="Q31" s="8" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:18">
       <c r="A32" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="33" ht="18" spans="4:15">
       <c r="D33" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="I33" s="2"/>
       <c r="L33" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="M33" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="N33" s="5" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="34" ht="18" spans="4:15">
       <c r="D34" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="N34" s="5" t="s">
         <v>316</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N34" s="5" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="35" ht="18" spans="4:15">
       <c r="D35" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="L35" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="L35" s="12" t="s">
+      <c r="M35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N35" s="5" t="s">
         <v>320</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="36" ht="18" spans="4:15">
       <c r="D36" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="L36" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="M36" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="37" ht="18" spans="4:15">
+      <c r="L37" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="M37" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="37" ht="18" spans="4:15">
-      <c r="L37" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="M37" s="7" t="s">
+    <row r="38" ht="18" spans="4:15">
+      <c r="L38" s="13" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="38" ht="18" spans="4:15">
-      <c r="L38" s="7" t="s">
+      <c r="M38" s="7" t="s">
         <v>326</v>
-      </c>
-      <c r="M38" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="N38" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="39" ht="18" spans="4:15">
       <c r="L39" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="N39" t="s">
         <v>329</v>
       </c>
-      <c r="M39" s="7" t="s">
+    </row>
+    <row r="40" ht="18" spans="4:15">
+      <c r="L40" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="N39" s="5" t="s">
+      <c r="M40" s="7" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="40" ht="18" spans="4:15">
-      <c r="L40" s="13" t="s">
+      <c r="N40" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="M40" s="13" t="s">
+    </row>
+    <row r="41" ht="18" spans="4:15">
+      <c r="L41" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="N40" s="14" t="s">
+      <c r="M41" s="13" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="41" ht="18" spans="4:15">
-      <c r="L41" s="7" t="s">
+      <c r="N41" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="M41" s="7" t="s">
+    </row>
+    <row r="42" ht="18" spans="4:15">
+      <c r="L42" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="N41" s="14" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="42" ht="15.6" spans="4:15">
-      <c r="L42" s="8" t="s">
+      <c r="M42" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="M42" s="8" t="s">
+      <c r="N42" s="14" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="43" ht="15.6" spans="4:15">
+      <c r="L43" s="8" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="43" ht="18" spans="4:15">
-      <c r="L43" s="7" t="s">
+      <c r="M43" s="8" t="s">
         <v>339</v>
-      </c>
-      <c r="M43" s="7" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="44" ht="18" spans="4:15">
       <c r="L44" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="M44" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="M44" s="7" t="s">
+    </row>
+    <row r="45" ht="18" spans="4:15">
+      <c r="L45" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="N44" s="15" t="s">
+      <c r="M45" s="7" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="45" spans="4:15">
-      <c r="L45" t="s">
+      <c r="N45" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="M45" t="s">
+    </row>
+    <row r="46" spans="4:15">
+      <c r="L46" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="46" ht="18" spans="4:15">
-      <c r="L46" s="2" t="s">
+      <c r="M46" t="s">
         <v>346</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="47" ht="18" spans="4:15">
       <c r="L47" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="M47" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="O47" t="s">
         <v>349</v>
       </c>
-      <c r="N47" t="s">
+    </row>
+    <row r="48" ht="18" spans="4:15">
+      <c r="L48" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="O47" t="s">
+      <c r="M48" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="48" ht="18" spans="4:15">
-      <c r="L48" s="7" t="s">
+      <c r="N48" t="s">
         <v>352</v>
       </c>
-      <c r="M48" s="2" t="s">
+    </row>
+    <row r="49" ht="18" spans="12:15">
+      <c r="L49" s="7" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="49" ht="15" spans="12:15">
-      <c r="L49" s="16" t="s">
+      <c r="M49" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="M49" s="17" t="s">
+    </row>
+    <row r="50" ht="18" spans="12:15">
+      <c r="L50" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="N49" t="s">
+      <c r="M50" s="17" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="50" ht="18" spans="12:15">
-      <c r="L50" t="s">
+      <c r="N50" t="s">
         <v>357</v>
       </c>
-      <c r="M50" s="18" t="s">
+      <c r="O50" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="O50" s="2" t="s">
+    </row>
+    <row r="51" ht="16.2" spans="12:15">
+      <c r="L51" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="51" ht="16.2" spans="12:15">
-      <c r="L51" s="19" t="s">
+      <c r="M51" s="18" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="52" ht="16.2" spans="12:15">
+      <c r="L52" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="M51" s="18" t="s">
+      <c r="M52" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="52" ht="15.6" spans="12:15">
-      <c r="L52" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="M52" s="8" t="s">
+    <row r="53" ht="15.6" spans="12:15">
+      <c r="L53" s="8" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="53" ht="18" spans="12:15">
-      <c r="L53" s="2" t="s">
+      <c r="M53" s="8" t="s">
         <v>362</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="54" ht="18" spans="12:15">
       <c r="L54" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="M54" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="55" ht="18" spans="12:15">
       <c r="L55" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="M55" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="56" ht="18" spans="12:15">
       <c r="L56" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="M56" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="N56" s="15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="57" ht="18" spans="12:15">
       <c r="L57" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="N57" s="15" t="s">
         <v>371</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="N57" s="15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="58" ht="18" spans="12:15">
       <c r="L58" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="M58" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="M58" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>375</v>
+      <c r="N58" s="15" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="59" ht="18" spans="12:15">
       <c r="L59" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="N59" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="60" ht="18" spans="12:15">
       <c r="L60" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="N60" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="M60" t="s">
+    </row>
+    <row r="61" ht="18" spans="12:15">
+      <c r="L61" s="2" t="s">
         <v>380</v>
       </c>
-    </row>
-    <row r="61" spans="12:15">
-      <c r="L61" t="s">
+      <c r="M61" t="s">
         <v>381</v>
-      </c>
-      <c r="M61" t="s">
-        <v>382</v>
-      </c>
-      <c r="N61" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="62" spans="12:15">
       <c r="L62" t="s">
+        <v>382</v>
+      </c>
+      <c r="M62" t="s">
+        <v>383</v>
+      </c>
+      <c r="N62" t="s">
         <v>384</v>
-      </c>
-      <c r="M62" t="s">
-        <v>385</v>
-      </c>
-      <c r="N62" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="63" spans="12:15">
       <c r="L63" t="s">
+        <v>385</v>
+      </c>
+      <c r="M63" t="s">
+        <v>386</v>
+      </c>
+      <c r="N63" t="s">
         <v>387</v>
-      </c>
-      <c r="M63" t="s">
-        <v>388</v>
-      </c>
-      <c r="N63" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="64" spans="12:15">
       <c r="L64" t="s">
+        <v>388</v>
+      </c>
+      <c r="M64" t="s">
+        <v>389</v>
+      </c>
+      <c r="N64" t="s">
         <v>390</v>
-      </c>
-      <c r="M64" t="s">
-        <v>391</v>
-      </c>
-      <c r="N64" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="65" spans="12:14">
       <c r="L65" t="s">
+        <v>391</v>
+      </c>
+      <c r="M65" t="s">
+        <v>392</v>
+      </c>
+      <c r="N65" t="s">
         <v>393</v>
       </c>
-      <c r="M65" t="s">
+    </row>
+    <row r="66" spans="12:14">
+      <c r="L66" t="s">
         <v>394</v>
       </c>
-      <c r="N65" t="s">
+      <c r="M66" t="s">
         <v>395</v>
+      </c>
+      <c r="N66" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -4477,69 +4489,69 @@
   <sheetData>
     <row r="2" ht="18" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:9">
       <c r="A3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" ht="18" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:9">
@@ -4562,39 +4574,39 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C4" s="5"/>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C5" s="6">
         <v>11293</v>
@@ -4602,67 +4614,67 @@
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -4679,26 +4691,26 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -4720,136 +4732,136 @@
   <sheetData>
     <row r="2" ht="18" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
